--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103289</v>
+        <v>103296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103296</v>
+        <v>103297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103297</v>
+        <v>103299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98369</v>
+        <v>98371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103299</v>
+        <v>103303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98371</v>
+        <v>98375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103303</v>
+        <v>103304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98375</v>
+        <v>98376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103304</v>
+        <v>103306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103306</v>
+        <v>103308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98378</v>
+        <v>98380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103308</v>
+        <v>103312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103312</v>
+        <v>103325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98382</v>
+        <v>98386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103325</v>
+        <v>103328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98386</v>
+        <v>98389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>125831277</v>
       </c>
       <c r="B3" t="n">
-        <v>103328</v>
+        <v>103337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125831697</v>
       </c>
       <c r="B4" t="n">
-        <v>98389</v>
+        <v>98398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,74 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88125113</v>
+        <v>125831277</v>
       </c>
       <c r="B2" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomsjön, Srm</t>
+          <t>Lomsjön SSO om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589225.1393968305</v>
+        <v>589142</v>
       </c>
       <c r="R2" t="n">
-        <v>6548452.564118165</v>
+        <v>6548554</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,25 +762,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Chad Donaldson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Chad Donaldson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125831277</v>
+        <v>88125209</v>
       </c>
       <c r="B3" t="n">
-        <v>103337</v>
+        <v>56689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,41 +798,57 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>706</v>
+        <v>206046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomsjön SSO om, Srm</t>
+          <t>Lomsjön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589142</v>
+        <v>589225</v>
       </c>
       <c r="R3" t="n">
-        <v>6548554</v>
+        <v>6548453</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,12 +872,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sprang över promenadvagen ca 15m från mig.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,39 +901,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>hygge</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Chad Donaldson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Chad Donaldson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125831697</v>
+        <v>88125113</v>
       </c>
       <c r="B4" t="n">
-        <v>98398</v>
+        <v>56905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,41 +930,58 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>208260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomsjön SSO om, Srm</t>
+          <t>Lomsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589128</v>
+        <v>589225</v>
       </c>
       <c r="R4" t="n">
-        <v>6548589</v>
+        <v>6548453</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,12 +1005,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,23 +1033,442 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Vägslänt skogsväg</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Chad Donaldson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Chad Donaldson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125831697</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lomsjön SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589128</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6548589</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt skogsväg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125831825</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lomsjön SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589240</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6548449</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägren skogsväg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125831834</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lomsjön SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589240</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6548449</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägren skogsväg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125873841</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lomsjön SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589240</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6548449</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1148-2025 artfynd.xlsx
+++ b/artfynd/A 1148-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88125209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88125113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831697</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831825</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125831834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,8 +1504,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125873841</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>